--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/07 12:28:03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>58823</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>500000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>58823.53</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58823.53</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>58823</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>58823.53</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.53</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/07 10:57:55</t>
+          <t>07/15 13:16:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,12 +95,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58823.53</t>
+          <t>10588.24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>张黎</t>
+          <t>邓迎春</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>07/07 12:28:03</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>58823</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>90000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>10588.24</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>58823.53</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>58823</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.53</t>
+          <t>10588.24</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/15 14:22:07</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>90000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>90000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10588.24</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>10588</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>10588.24</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.24</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/15 13:16:56</t>
+          <t>07/24 11:11:31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,22 +90,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>20481.93</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>邓迎春</t>
+          <t>卢华</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>07/15 14:22:07</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>10588</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>170000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>20481.93</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10588.24</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10588</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.24</t>
+          <t>20481.93</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/24 12:13:55</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>20481</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>170000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>170000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20481.93</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>20481</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>20481.93</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.93</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/24 11:11:31</t>
+          <t>07/27 11:23:18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>215000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,17 +95,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>25903.61</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>卢华</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>07/24 12:13:55</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>20481</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>215000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>25903.61</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20481.93</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20481</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.93</t>
+          <t>25903.61</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/27 12:29:51</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>25903</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>215000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>25903.61</t>
+          <t>215000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25903.61</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>25903</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>25903.61</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.61</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -75,210 +75,252 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07/27 15:17:33</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>10714.29</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>葛长跃</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>07/27 11:23:18</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>215000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>25903.61</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>王琪</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>07/27 12:29:51</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>25903</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>215000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>25903.61</t>
+          <t>305000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>36617.9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>25903</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.61</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>10714.9</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -244,83 +244,110 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>07/27 16:38:35</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>10714</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>07/27 12:29:51</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>25903</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>305000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>36617.9</t>
+          <t>305000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>25903</t>
+          <t>36617.9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>36617</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>10714.9</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.9</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/27 15:17:33</t>
+          <t>08/04 13:42:31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,17 +90,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10714.29</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>王琪</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -114,240 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>07/27 11:23:18</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>215000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>25903.61</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>王琪</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/27 16:38:35</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>10714</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/27 12:29:51</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25903</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t>100000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>12048.19</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>305000</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>36617.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>36617</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>0.9</t>
+          <t>12048.19</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>08/04 15:01:25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12048.19</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>12048.19</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>-799.81</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>08/04 15:01:25</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>12848</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>12048.19</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12848</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>-799.81</t>
+          <t>12048.19</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>08/04 15:01:41</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12048</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12048.19</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12048</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>12048.19</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.19</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/04 13:42:31</t>
+          <t>08/07 13:37:02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>30120.48</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>08/04 15:01:41</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>12048</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>250000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>30120.48</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12048</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.19</t>
+          <t>30120.48</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>08/07 15:15:17</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>30120</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>250000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>250000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30120.48</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>30120</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>30120.48</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.48</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/07 13:37:02</t>
+          <t>08/11 14:11:24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,17 +95,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>10843.37</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>王琪</t>
+          <t>葛长跃</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>08/07 15:15:17</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>30120</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>90000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>10843.37</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>30120.48</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>30120</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.48</t>
+          <t>10843.37</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>08/11 15:41:53</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10843</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>90000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>90000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10843.37</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>10843</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>10843.37</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.37</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/11 14:11:24</t>
+          <t>08/12 14:48:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,12 +95,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>葛长跃</t>
+          <t>姚治文</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>08/11 15:41:53</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>10843</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>80000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>9638.55</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10843.37</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10843</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.37</t>
+          <t>9638.55</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>08/12 15:50:44</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>9638</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>80000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>80000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9638.55</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>9638</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>9638.55</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.55</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/12 14:48:22</t>
+          <t>08/23 09:56:14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,17 +90,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>姚治文</t>
+          <t>马书文</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>08/12 15:50:44</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>9638</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>9638</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.55</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>08/23 11:10:42</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>11904.76</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.76</t>
         </is>
       </c>
     </row>
